--- a/docs/vue-ensemble-transaction-document/ig/submissionSetToPDSM.xlsx
+++ b/docs/vue-ensemble-transaction-document/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:02:39+00:00</t>
+    <t>2026-07-15T13:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/vue-ensemble-transaction-document/ig/submissionSetToPDSM.xlsx
+++ b/docs/vue-ensemble-transaction-document/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:04:45+00:00</t>
+    <t>2026-07-15T13:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
